--- a/lessons-8-stats/Кілт_статистика.xlsx
+++ b/lessons-8-stats/Кілт_статистика.xlsx
@@ -525,22 +525,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>СОР 1</t>
+          <t>БЖБ 1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>СОР 2</t>
+          <t>БЖБ 2</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>СОР 3</t>
+          <t>БЖБ 3</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>СОЧ</t>
+          <t>ТЖБ</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
